--- a/GearSage-client/pkgGear/data_raw/raid_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/raid_rod_import.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.83203125" customWidth="1" min="1" max="1"/>
@@ -518,50 +518,55 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>fit_style_tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>images</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>series_positioning</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>main_selling_points</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>official_reference_price</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>market_status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>player_positioning</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>player_selling_points</t>
         </is>
@@ -598,41 +603,46 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/raid_rods/RR1000_Gladiator_Maximum.jpg</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Fresh Water / Bass</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>■MAXIMUMコンセプト 目指したのは「何でも無難にこなすロッド」では達することのできない極致。 バーサタイル性を排除し、ある特定のオペレーションにおいてズバ抜けた性能を発揮する特化型ロッドシリーズが完成。 その名もGLADIATOR MAXIMUM。 GLADIATOR史上、もっとも独裁的で我儘な皇帝「MAXIMUM」がついに動き出す。</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>¥55,000-¥65,000（税抜）</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>■MAXIMUMコンセプト 目指したのは「何でも無難にこなすロッド」では達することのできない極致。 バーサタイル性を排除し、ある特定のオペレーションにおいてズバ抜けた性能を発揮する特化型ロッドシリーズが完成。 その名もGLADIATOR MAXIMUM。 GLADIATOR史上、もっとも独裁的で我儘な皇帝「MAXIMUM」がついに動き出す。
 The baddest emperor ever in the Gladiator series, "MAXIMUM" is here to reign supreme. ■ MAXIMUM Concept Designed to reach a level unattainable with "an all-rounder rod". The Maximum series eliminates versatility and delivers the highest performance for each specific use. Named the GLADIATOR MAXIMUM. The baddest emperor ever in the Gladiator series, "MAXIMUM" is here to reign supreme.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>淡水 Bass / 特化型技法竿</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>按單一技法強化的高階 Bass 竿系，適合精細、硬餌、強力 cover 與大餌等明確場景分工。</t>
         </is>
@@ -669,30 +679,35 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>bass</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>https://static.gearsage.club/gearsage/Gearimg/images/raid_rods/RR1001_Gladiator_Anti.jpg</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Fresh Water / Bass</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>■What means an ANTI? ORIGINAL GLADIATORの対極に位置するロッドを作りたい。ORIGINAL GLADIATORがミッションであるとするならば、竿本来の仕事を自動的にこなしてくれるオートマチックなロッドを作りたい。 そんな想いからスタートしたプロジェクト。 心血注いでORIGINAL GLADIATORを生み出した我々自らが、あえて真っ向から否定し、別角度から導き出したもうひとつの答え。 ORIGINAL GLADIATORを否定する、もうひとつのGLADIATOR 反乱因子「A</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>¥35,500-¥45,000（税抜）</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>官网展示</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>■What means an ANTI? ORIGINAL GLADIATORの対極に位置するロッドを作りたい。ORIGINAL GLADIATORがミッションであるとするならば、竿本来の仕事を自動的にこなしてくれるオートマチックなロッドを作りたい。 そんな想いからスタートしたプロジェクト。 心血注いでORIGINAL GLADIATORを生み出した我々自らが、あえて真っ向から否定し、別角度から導き出したもうひとつの答え。 ORIGINAL GLADIATORを否定する、もうひとつのGLADIATOR 反乱因子「ANTI」ここに誕生。
 ■ANTI'S 3 Concepts… ●Concept-1. 「キャスト」「リトリーブ」「ファイト」全てにおいてアングラーを高アシスト(ロッド自体が仕事を完璧にこなす万能型中弾性ブランクス) ・釣り行為においてロッドが担うオペレーション「キャスト」「リトリーブ」「フッキング~ファイト」そのすべてにおいて、ロッド自体がその仕事を完璧にこなす。キャスト時にはブランクスがルアーの重量によってしっかりと曲がり、その反発力によって正確にかつ軽い力でルアーを飛ばす。リトリーブ時には突っ張りすぎずルアーが送る信号をアングラーに正確に伝達。フッキング時にはブランクス全体が生み出すトルクによって針が魚のアゴを貫く。ファイト時にはティップ~バットエンドに至るそのすべてが魚の引きに比例したトルクを発揮。魚が引くほどに・竿が曲がるほどにブランクが元に戻ろうとする力が溢れ出し、自然と魚を手繰り寄せてしまうオートマチックブランクス。アングラーの腕となるのではなく、アングラーを強力にアシストしネクストレヴェルに押し上げるまさにパワーアームのような強化ツールです。 ●Concept-2. 超広守備範囲(メインオペレーションを軸に幅広い対応領域) ・初めて訪れるフィールド、ましてや岸釣りとなると、専用機を何本も持ち歩く訳にはいきません。岸釣りのアドヴァンテージとも言える「機動力」を犠牲にすることになります。もし1本のロッドで、メインオペレーション以外にもある程度高次元にこなせるロッドがあったら、それだけで心強い武器になるでしょう。Antiは、そのブランクス特性によって極めて幅広い守備範囲を確保しています。 ●Concept-3. 高性能を低価格で提供 ・Antiシリーズは竿本来の役割を一から見直し、アングラー側にふりかかるあらゆる負担や要求される技能をブランクスによって補うことで、誰もが扱い易く高次元のオペレーションを遂行できるオートマチックなロッドに仕上げています。それが上級者であっても、さらに一段階上の釣りが体感できるAntiの性能の高さに驚くことでしょう。我々が目指したのは、自信作であるこのAntiが持つ「竿本来の性能」を、より多くのアングラーに味わってもらうこと。低価格実現のため、ブランクス性能に影響を及ぼしにくいガイドをステンレス化(TOPガイドはチタンフレーム)。ハイグレードコルクをEVA化。ブランクス性能及び所有感をもたらす装飾の質を下げることなく製造コストを抑えることに成功しました。Antiは、「低価格」でありながら「高性能」を体感できるシリーズなのです。
@@ -700,12 +715,12 @@
 ■ANTI'S 3 Concepts… ●Concept-1. Exceptional assistance of the angler during the "cast" "retrieve" "fight" (All-around mid-modulus blank that perfectly performs all motions) ・For all operations handed by the rod from "cast" "retrieve" "hookset and fight", the rod itself completes the job. When cast, the blank fully bends with the weight of the lure and sends the lure flying with accuracy and little power. On the retrieve, without pulling the lure too hard, the angler can accurately feel the signals at the end of the line. On the hookset, the torque generated from the entire blank penetrates the hook into the fish's jaw. During the fight, torque is generated from the rod tip to the butt end in relation to the fish's pull. As the fish pulls harder and bends the rod, the blank exerts power to bounce back, which makes the blank "automatic" in landing fish. Rather than becoming the angler's arm, the blank becomes a power arm that assists the angler in reaching the next level of fishing. ●Concept-2. Ultimate versatility (beyond its primary strengths) ・When visiting new waters, especially bank fishing, it's impractical to carry multiple special-purpose rods. Doing so might sacrifice the advantage of bank fishing which is "mobility". The focus became developing a rod that performed its primary function and serve secondary functions at a high level. The ANTI with its unique blank specifications enables this exceptional versatility. ●Concept-3. High performance at a low cost ・With the ANTI series, we reassessed what is truly needed in a rod and selected blanks that compensate for various field conditions and angler skill levels. The result is an "automatic" rod that delivers easy handling and high performance for anyone. Even advanced anglers will be amazed at how the ANTI will elevate their game. We want everyone to try our masterpiece, the ANTI, which brings the focus back on a "rod's core capabilities". To provide it at a low cost but keep blank performance intact, stainless-steel guides (top guide is titanium frame) and EVA grip (instead of high-grade cork) were used. The final product has blank performance and quality aesthetics that anglers can appreciate, while manufacturing costs were kept low. Feel the "high performance" of the ANTI series at a "low cost".</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>淡水 Bass / 泛用輔助型竿系</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>以易用和高守備範圍為核心，覆蓋岸釣與船釣常見 Bass 技法，適合按子型號細分用途。</t>
         </is>

--- a/GearSage-client/pkgGear/data_raw/raid_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/raid_rod_import.xlsx
@@ -474,10 +474,11 @@
     <col width="18.83203125" customWidth="1" min="11" max="11"/>
     <col width="18.83203125" customWidth="1" min="12" max="12"/>
     <col width="18.83203125" customWidth="1" min="13" max="13"/>
-    <col width="18.83203125" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
     <col width="90.83203125" customWidth="1" min="15" max="15"/>
     <col width="18.83203125" customWidth="1" min="16" max="16"/>
     <col width="18.83203125" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -737,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR33"/>
+  <dimension ref="A1:AS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.83203125" customWidth="1" min="1" max="1"/>
@@ -782,7 +783,7 @@
     <col width="16.83203125" customWidth="1" min="40" max="40"/>
     <col width="16.83203125" customWidth="1" min="41" max="41"/>
     <col width="90.83203125" customWidth="1" min="42" max="42"/>
-    <col width="16.83203125" customWidth="1" min="43" max="43"/>
+    <col width="90.83203125" customWidth="1" min="43" max="43"/>
     <col width="16.83203125" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
@@ -999,10 +1000,15 @@
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>product_technical</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>Extra Spec 1</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Extra Spec 2</t>
         </is>
@@ -1124,8 +1130,9 @@
 ■TIP部分:30tカーボンソリッドTIPを採用。 ■リールシート:細すぎず太すぎない絶妙なグリッピングを実現したRAID JAPANオリジナルリールシート(RJCS01)を採用。やや短めに設定されたトリガー部分は、キャスト~リーリングの際にスムーズに持ち替える事が可能。また、トリガー前の部分の指が遊ぶ(浮く)ことなく、しっかりと握り込むようなグリッピングが可能です。</t>
         </is>
       </c>
-      <c r="AQ2" s="1" t="str"/>
+      <c r="AQ2" s="1" t="inlineStr"/>
       <c r="AR2" s="1" t="str"/>
+      <c r="AS2" s="1" t="str"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1241,8 +1248,9 @@
 With such a drastic taper, it may not seem versatile, but it surprisingly covers everything from heavy drop shot rigs, free rigs, light Texas, light backslide worms, and heavy Neko rigs. It works especially well with Egu-Dama Type-Cover and Level jigs. Where power-finesse and PE line combo don't work, the BISHOP is perfect for "hanging" rigs around hard structure for effortless casting and maneuvering.</t>
         </is>
       </c>
-      <c r="AQ3" s="1" t="str"/>
+      <c r="AQ3" s="1" t="inlineStr"/>
       <c r="AR3" s="1" t="str"/>
+      <c r="AS3" s="1" t="str"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1360,8 +1368,9 @@
 ※1…GLADIATOR、GLADIATOR Technix、GLADIATOR Anti、GLADIATOR MAXIMUMの全モデル含む。</t>
         </is>
       </c>
-      <c r="AQ4" s="1" t="str"/>
+      <c r="AQ4" s="1" t="inlineStr"/>
       <c r="AR4" s="1" t="str"/>
+      <c r="AS4" s="1" t="str"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1476,12 +1485,13 @@
 The blank is custom tuned for heavy cover with bait finesse tackle, and although listed as "H" (heavy) power, it comes equipped with a sensitive solid tip. Even with a solid tip, the pressure dissipates along the entire blank. From casting light rigs accurately into cover, gently controlling it, letting the fish eat, and pulling it out from cover, the entire range of motions is performed without a glitch. THE MAXX sets the standard for next-generation heavy-power rods.</t>
         </is>
       </c>
-      <c r="AQ5" s="1" t="inlineStr">
+      <c r="AQ5" s="1" t="inlineStr"/>
+      <c r="AR5" s="1" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 14件; 场景: ため池 / 五三川 / リザーバー</t>
         </is>
       </c>
-      <c r="AR5" s="1" t="inlineStr">
+      <c r="AS5" s="1" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: レベルバイブ (レイドジャパン) / ヒラタイラー 3.7インチ (レイドジャパン)</t>
         </is>
@@ -1602,8 +1612,9 @@
           <t>全てはバスを釣る為に… 無駄を全て削ぎ落し洗練されたブランクスに、現代のバスフィッシングに求められる要素を落とし込んだ「THE MAXX 改」。 すでに完成の域に達していたTHE MAXXに、最先端の素材やノウハウを凝縮。デザイン面においても徹底的に追い込んだ結果、約20gもの軽量化に成功。破断強度とバットパワーをUPした7フィート・ヘビーアクション(SOLID TIP)にも関わらずその自重わずか101gを実現しています。その軽さからくる圧倒的なまでの軽快感は、異次元とも言える操作性と感度を手に入れました。極限の軽量化によってTHE MAXXよりも軽いリグにまで対応、下限が広がると同時にバットパワーが上がったことにより使えるルアー(リグウエイト)の上限自体は広がっています。 基本はワーミング特化型。THE MAXXから継承したやや長めの30t SOLID TIPとの組み合わせによって一部ムービング系の釣りもフォローできる適応能力の高さを持ち合わせています。 時代が求めたファクトリーチューンモデル「THE MAXX 改」、金森隆志の右腕から金森隆志の分身にまで昇華。</t>
         </is>
       </c>
-      <c r="AQ6" s="1" t="str"/>
+      <c r="AQ6" s="1" t="inlineStr"/>
       <c r="AR6" s="1" t="str"/>
+      <c r="AS6" s="1" t="str"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1720,12 +1731,13 @@
           <t>GLADIATOR Antiシリーズで好評を博したGA-72HC「King Heavy」を2インチショート化、高弾性化した上でパワーを1ランクUPして生まれ変わったのが「MAXX JACK」。 さらなるパワーフィッシングに対応するHeavy Plusではあるものの、ただ硬くて強い竿ではありません。硬いのに曲がる、硬いのに粘り強い、トルク溢れるパワーロッドに仕上がっています。 ビッグベイトやスイムベイトによる横方向のパワーゲーム、ラバージグやテキサスリグなどを使用した縦方向のパワーゲームにプラスして、MUSCLE WIRE / GHOST WIRE NEXT LEVELにFISHROLLER(3" / 4")を装着したバマストにも対応。フルチューブラーの高弾性ブランクスはTIPが垂れ過ぎず、ヘビーウエイトのルアーのキャスト~操作において抜群の使用感を得ることができます。 ヘビーロッドのバーサタイル性をMAXまで高めたロッドが「MAXX JACK」です。</t>
         </is>
       </c>
-      <c r="AQ7" s="1" t="inlineStr">
+      <c r="AQ7" s="1" t="inlineStr"/>
+      <c r="AR7" s="1" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 16件; 场景: ため池 / 五三川 / 霞ヶ浦水系,桜川,花室川,備前川,小野川</t>
         </is>
       </c>
-      <c r="AR7" s="1" t="inlineStr">
+      <c r="AS7" s="1" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: ヒラタイラー 3.7インチ (レイドジャパン) / レベルバイブ (レイドジャパン)</t>
         </is>
@@ -1848,12 +1860,13 @@
 ■TIP部分:30tカーボンソリッドTIPを採用。 ■リールシート:細すぎず太すぎない絶妙なグリッピングを実現したRAID JAPANオリジナルリールシート(RJCS01)を採用。やや短めに設定されたトリガー部分は、キャスト~リーリングの際にスムーズに持ち替える事が可能。また、トリガー前の部分の指が遊ぶ(浮く)ことなく、しっかりと握り込むようなグリッピングが可能です。</t>
         </is>
       </c>
-      <c r="AQ8" s="1" t="inlineStr">
+      <c r="AQ8" s="1" t="inlineStr"/>
+      <c r="AR8" s="1" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 10件; 场景: 霞ヶ浦 / リザーバー / 五三川</t>
         </is>
       </c>
-      <c r="AR8" s="1" t="inlineStr">
+      <c r="AS8" s="1" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: ゴーストワイヤー プロト , フィッシュローラー 3インチ (レイドジャパン) / ゴーストワイヤー , フィッシュローラー 3インチ 4インチ (レイドジャパン)</t>
         </is>
@@ -1975,8 +1988,9 @@
 ■ガイド:全ガイドに軽量・高感度なFuji工業製チタンフレーム/トルザイトガイドを採用。 ■リールシート:細すぎず太すぎない絶妙なグリッピングを実現したRAID JAPANオリジナルリールシート(RJCS01)を採用。やや短めに設定されたトリガー部分は、キャスト~リーリングの際にスムーズに持ち替えることが可能。また、トリガー前の部分の指が遊ぶ(浮く)ことなく、しっかりと握り込むようなグリッピングが可能です。 ■コルク&amp;EVA GRIP: ロングキャストの際、どんな握り方でもしっかりと引手に力が入るように、全体的にやや太目なストレートGRIPを採用。キャストを繰り返すほどに実感できる絶妙な太さに設計しています。グリッピングした際に触れる箇所は軽量かつ高感度なコルク、リアには適度な重量によってロッドTIPが自然に上を向くバランスを求めたEVAのハイブリッド。</t>
         </is>
       </c>
-      <c r="AQ9" s="1" t="str"/>
+      <c r="AQ9" s="1" t="inlineStr"/>
       <c r="AR9" s="1" t="str"/>
+      <c r="AS9" s="1" t="str"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2092,12 +2106,13 @@
 The blank casts lightweight rigs accurately and breathes life into rigs with rod action. The fish won't even realize they've been caught after a bite; it's that sort of magic built into this blank. Both XL/UL models deliver exceptional performance on all lightweight rigs, but the SOLID MAXX XL excels in delicate shaking on one spot. The SOLID MAXX UL works best for tossing finesse rigs into cover in an up-tempo style.</t>
         </is>
       </c>
-      <c r="AQ10" s="1" t="inlineStr">
+      <c r="AQ10" s="1" t="inlineStr"/>
+      <c r="AR10" s="1" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 3件; 场景: さめうら湖 / 与田浦</t>
         </is>
       </c>
-      <c r="AR10" s="1" t="inlineStr">
+      <c r="AS10" s="1" t="inlineStr">
         <is>
           <t>白名单路亚信号: worm / finesse; 样本路亚: フィッシュローラー 4インチ (レイドジャパン) / ホバリングバグ ECO (ティムコ)</t>
         </is>
@@ -2217,12 +2232,13 @@
 The blank casts lightweight rigs accurately and breathes life into rigs with rod action. The fish won't even realize they've been caught after a bite; it's that sort of magic built into this blank. Both XL/UL models deliver exceptional performance on all lightweight rigs, but the SOLID MAXX XL excels in delicate shaking on one spot. The SOLID MAXX UL works best for tossing finesse rigs into cover in an up-tempo style.</t>
         </is>
       </c>
-      <c r="AQ11" s="1" t="inlineStr">
+      <c r="AQ11" s="1" t="inlineStr"/>
+      <c r="AR11" s="1" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 4件; 场景: 坂部池 / 南川ダム / 門池</t>
         </is>
       </c>
-      <c r="AR11" s="1" t="inlineStr">
+      <c r="AS11" s="1" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: ミドストジグヘッド 2.5g (deps) , フィネスティック 3.5インチ (レイドジャパン) / ヘッドシェイカー 4インチ (エバーグリーン)</t>
         </is>
@@ -2341,12 +2357,13 @@
 The ultimate rod that becomes not just an extension of your arm, but an extension beyond your fingertips.</t>
         </is>
       </c>
-      <c r="AQ12" s="1" t="inlineStr">
+      <c r="AQ12" s="1" t="inlineStr"/>
+      <c r="AR12" s="1" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 6件; 场景: ため池 / 高滝湖 / 燧ヶ池</t>
         </is>
       </c>
-      <c r="AR12" s="1" t="inlineStr">
+      <c r="AS12" s="1" t="inlineStr">
         <is>
           <t>白名单路亚信号: worm / finesse; 样本路亚: 2WAY (レイドジャパン) / フィッシュローラー マイクロ , マイクロ 2WAY (レイドジャパン)</t>
         </is>
@@ -2468,8 +2485,9 @@
 ※1・・・GLADIATOR、GLADIATOR Technix、GLADIATOR Anti、GLADIATOR MAXIMUMの全モデル含む。</t>
         </is>
       </c>
-      <c r="AQ13" s="1" t="str"/>
+      <c r="AQ13" s="1" t="inlineStr"/>
       <c r="AR13" s="1" t="str"/>
+      <c r="AS13" s="1" t="str"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2583,12 +2601,13 @@
 ■TIP部分:30tロングカーボンソリッドTIPを採用。 ■ガイド:全ガイドに軽量・高感度なFuji工業製チタンフレーム/トルザイトガイドを採用。 ■リールシート:Fuji工業製リールシートIPS16を採用。様々なグリッピングに対応。</t>
         </is>
       </c>
-      <c r="AQ14" s="1" t="inlineStr">
+      <c r="AQ14" s="1" t="inlineStr"/>
+      <c r="AR14" s="1" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 9件; 场景: 高滝湖 / 霞ヶ浦 / ため池</t>
         </is>
       </c>
-      <c r="AR14" s="1" t="inlineStr">
+      <c r="AS14" s="1" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: like2.5 (エンジン) / アヴィ 35 (レイドジャパン)</t>
         </is>
@@ -2713,8 +2732,9 @@
 勿論、こだわりはティップだけでは無く、極めて伸びの少ないPEラインの突っ張り感を吸収し、バスを必要以上に暴れさせず、ラインをブレイクから守る柔軟なテーパーや、いざという時のパワー感などトータルバランスに優れたセッティングになっている事は言うまでもありません。</t>
         </is>
       </c>
-      <c r="AQ15" s="1" t="str"/>
+      <c r="AQ15" s="1" t="inlineStr"/>
       <c r="AR15" s="1" t="str"/>
+      <c r="AS15" s="1" t="str"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2837,8 +2857,9 @@
 フロロカーボンラインだけでなく、近年使用率の高くなったPEラインでもストレスないガイドセッティングは、よりボリュームのあるリグ / より遠距離 / よりディープでの使用にも対応。 近年、フィールド / 季節問わずビッグバス攻略に必要不可欠なテクニックとなったパワーミドストのアプローチに特化したモデルです。</t>
         </is>
       </c>
-      <c r="AQ16" s="1" t="str"/>
+      <c r="AQ16" s="1" t="inlineStr"/>
       <c r="AR16" s="1" t="str"/>
+      <c r="AS16" s="1" t="str"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2957,12 +2978,13 @@
 For finesse techniques with worms and plugs, and for exceptional agility in both bank and boat fishing scenarios, the BF Tricker is a technical short rod that powerfully aids the angler for bait finesse techniques.</t>
         </is>
       </c>
-      <c r="AQ17" s="2" t="inlineStr">
+      <c r="AQ17" s="2" t="inlineStr"/>
+      <c r="AR17" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 3件; 场景: 野添溜池 / ポンド / 桜沼公園</t>
         </is>
       </c>
-      <c r="AR17" s="2" t="inlineStr">
+      <c r="AS17" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: ジャスターフィッシュ 3.5インチ (GETNET) / キッケルカーリー (DAIWA)</t>
         </is>
@@ -3087,12 +3109,13 @@
           <t>ハードベイトを軽快かつ快適に操る為のモデル「Black Viper」。 狙った場所へズバズバとキャストを決め、ハードプラグを自在に操り、ルアー毎のアクションを感じながら巻くことができるプラッギングをとことん楽しむための1本。 ハードベイトの中でもジャークベイトの釣りを主眼に置いて開発したBlack Viperは、ベーシックな80~120mmクラスのジャークベイトに命を吹き込みます。レギュラーテーパーの中に見え隠れするわずかな"TIPの張り"によって、ジャークベイトにキレのある力強いアクションを入力することができる上、しっかりとブランクが入るのでジャークのリズムが取りやすくなっています。ロッドワークの強弱でアクションが千変万化するジャークベイトを意のままに操縦できる珠玉の1本に仕上げました。 ジャークベイト以外にも、総重量5/8oz.前後までのクランクベイトやバイブレーション、ポッパー、ペンシルベイト、ワイヤーベイトまで幅広い巻きの釣りもこなすため、小~中規模フィールドで岸釣り/ボートでの釣りはもちろん、ショートレングス特有の取り回しの良さと操作性はレンタルボートフィールドでのハードベイトゲームにおいても重宝する1本です。</t>
         </is>
       </c>
-      <c r="AQ18" s="2" t="inlineStr">
+      <c r="AQ18" s="2" t="inlineStr"/>
+      <c r="AR18" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 3件; 场景: リザーバー / ため池</t>
         </is>
       </c>
-      <c r="AR18" s="2" t="inlineStr">
+      <c r="AS18" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait; 样本路亚: SKM (レイドジャパン) / ジャークリッパー (レイドジャパン)</t>
         </is>
@@ -3214,12 +3237,13 @@
 Knowing the limits of bait tackle for working light lures, RAID JAPAN was one of the first to propose the power bait finesse setup. If bait finesse is defined as covering the middle ground between finesse fishing on spinning gear and power fishing on bait gear, "Power Bait Finesse" covers the small area between bait finesse and bait gear. This high-performing model that we crowned the "Power Bait Finesse" certainly lives up to its name. Effective for bait finesse techniques that primarily use straight worm Neko rigs for rapid casting, deploying small rubber rigs in blind casts to get bites, and for plugs less than 10g. These tactics are made possible with 30t carbon solid tip, un-sanded blank, 4-axis carbon reinforcement, and original guide setting. In customizing the parts to the extreme, this model embodies high-octane and high control.</t>
         </is>
       </c>
-      <c r="AQ19" s="2" t="inlineStr">
+      <c r="AQ19" s="2" t="inlineStr"/>
+      <c r="AR19" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 6件; 场景: 霞ヶ浦 / 霞ヶ浦水系 / 天竜川</t>
         </is>
       </c>
-      <c r="AR19" s="2" t="inlineStr">
+      <c r="AS19" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: レベルバイブブースト 7g / ブレーバー2 (ボトムアップ)</t>
         </is>
@@ -3341,12 +3365,13 @@
 ■TOPガイドはT-KGST、#1~#6ガイドにはPKBSG、#7~#9ガイドにはPLKWSGで構成。PEライン使用時にも抜けが良く、高負荷に耐える強度も確保したセッティングです。</t>
         </is>
       </c>
-      <c r="AQ20" s="2" t="inlineStr">
+      <c r="AQ20" s="2" t="inlineStr"/>
+      <c r="AR20" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 9件; 场景: 霞ヶ浦 / 池 / 梨木公園</t>
         </is>
       </c>
-      <c r="AR20" s="2" t="inlineStr">
+      <c r="AS20" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: ダッジ (レイドジャパン) / マイクロダッジ ビッグ (レイドジャパン)</t>
         </is>
@@ -3469,12 +3494,13 @@
 Deploying mid-modulus carbon on the main cross section, unpainted and unpolished, and four axis butt section, the "smooth yet sharp" feel of the GLADIATOR Anti series is felt most on this model. It's best at working 7g~14g moving baits used most often in bass fishing as well as handling similar weight worms. As the rod bends like a bow, the casting feel is incredible. The lure's weight is firmly placed on the rod and cast with ultimate accuracy to the target area. The Joker will give you enjoyment in "casting" and "fishing" like you've never experienced before.</t>
         </is>
       </c>
-      <c r="AQ21" s="2" t="inlineStr">
+      <c r="AQ21" s="2" t="inlineStr"/>
+      <c r="AR21" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 13件; 场景: 倉敷川水系 / 淡路島野池 / 五三川</t>
         </is>
       </c>
-      <c r="AR21" s="2" t="inlineStr">
+      <c r="AS21" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: 大餌 / swimbait / moving bait / hard bait / worm / finesse; 样本路亚: レベルミノー (Raid Japan) / レベルバイブ ビッグ (レイドジャパン)</t>
         </is>
@@ -3600,12 +3626,13 @@
 As average catch sizes are increasing across the country, bigger and heavier lures are being used. Thus, anglers require heavier tackle, and this rod delivers strength and length beyond those expectations. The versatile Baltoro is a medium-heavy power rod that superbly works 10g~20g moving and soft baits while also delivering a unique balance of power and fine-tuned core strength. It delivers high performance in the bass fishing basics of "casting" and "hookset". Additionally, the rod length is kept the same as the lesser power Joker, and by also maintaining the same balance in grip shape and length, it keeps the same overall feel. This concept of keeping the same feel while increasing power is seen in the Transporter and Skywalker of the GLADIATOR Original series and has been a key concept of Raid Japan since our beginning.</t>
         </is>
       </c>
-      <c r="AQ22" s="2" t="inlineStr">
+      <c r="AQ22" s="2" t="inlineStr"/>
+      <c r="AR22" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 7件; 场景: 霞ヶ浦 / 小野川湖 / 京徳池公園</t>
         </is>
       </c>
-      <c r="AR22" s="2" t="inlineStr">
+      <c r="AS22" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: Frog / topwater / moving bait / hard bait / worm / finesse; 样本路亚: バギークロー (レイドジャパン) / フルスイング 5in (レイドジャパン)</t>
         </is>
@@ -3734,8 +3761,9 @@
 ※1・・・GLADIATORシリーズのG-63MLGCとG-69MGCはグラスソリッドTIPを採用。</t>
         </is>
       </c>
-      <c r="AQ23" s="2" t="str"/>
+      <c r="AQ23" s="2" t="inlineStr"/>
       <c r="AR23" s="2" t="str"/>
+      <c r="AS23" s="2" t="str"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3853,12 +3881,13 @@
 The versatile heavy-power rod, King Heavy is here. Unlike standard heavy-power rods that are hard and inflexible, the King Heavy delivers a unique combination of strength and flexibility for versatile power fishing with just a single rod. Even with lightweight rigs and small worms, the blank is specified to bend true to the load which allows stress-free casting and handling. Equally effective for pitching and side casting to short distances and maximizes its 7'2" length to make long distance casts just as simple. Employing a new carbon material for the first time in the GLADIATOR Anti series, the blank is constructed with a half polish to maximize performance. The blank has the right balance of sharpness and torque. Exceptional as a worming rod in cover and for long-range casting and handling of heavy Carolina rigs and heavy worms in open water. It's also effective for heavyweight moving baits and baits with strong water resistance. This is the ultimate versatile heavy-power rod.</t>
         </is>
       </c>
-      <c r="AQ24" s="2" t="inlineStr">
+      <c r="AQ24" s="2" t="inlineStr"/>
+      <c r="AR24" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 9件; 场景: 高山ダム / 七色ダム / 牛久沼</t>
         </is>
       </c>
-      <c r="AR24" s="2" t="inlineStr">
+      <c r="AS24" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: ダブルヘッダー (レイドジャパン) / タイニークラッシュ (DRT)</t>
         </is>
@@ -3982,12 +4011,13 @@
 And it's not just exceptional with big baits. A trademark of the Anti series, the highly versatile Diffuser works rubber jigs and Texas rigs through cover equally well.</t>
         </is>
       </c>
-      <c r="AQ25" s="2" t="inlineStr">
+      <c r="AQ25" s="2" t="inlineStr"/>
+      <c r="AR25" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 12件; 场景: 旧吉野川 / リザーバー / 野池</t>
         </is>
       </c>
-      <c r="AR25" s="2" t="inlineStr">
+      <c r="AS25" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: 大餌 / swimbait / moving bait / hard bait; 样本路亚: オサカナスライド 170 (レイドジャパン) / ビビッドクルーズ 170 (フィッシュアロー)</t>
         </is>
@@ -4115,12 +4145,13 @@
 Take the UNDERTAKER with you for a big bait experience like no other.</t>
         </is>
       </c>
-      <c r="AQ26" s="2" t="inlineStr">
+      <c r="AQ26" s="2" t="inlineStr"/>
+      <c r="AR26" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 3件; 场景: 正木池 / 釜無川 / 蛇沼</t>
         </is>
       </c>
-      <c r="AR26" s="2" t="inlineStr">
+      <c r="AS26" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: 大餌 / swimbait; 样本路亚: レイジーハード (イマカツ) , バラム ヴァリアンテ 255 (マドネス) / クラッシュジョーカー (DRT) , KRK 205 (カエス)</t>
         </is>
@@ -4242,12 +4273,13 @@
 In today's highly pressured fields, light rigs are becoming mandatory to get fish to eat. The mastermind behind catching such battle-hardened fish is the Fixer. The blank combines 30t carbon solid tip selected down to 1mm and un-sanded finish. With seamlessly connected sections that make a smooth bend, any ultra-fine movements made by the angler transmit directly to the rig, and vice versa. The solid tip directly and accurately sends information back to the angler. FUJI IPS seat is equipped for a soft grip that enables "zero-finger style" to disguise line and impart a delicate action. The Fixer is an offensive-minded finesse rod that gets fish to eat under any circumstance.</t>
         </is>
       </c>
-      <c r="AQ27" s="2" t="inlineStr">
+      <c r="AQ27" s="2" t="inlineStr"/>
+      <c r="AR27" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 6件; 场景: 霞ヶ浦水系 / 遠賀川 / 生板池</t>
         </is>
       </c>
-      <c r="AR27" s="2" t="inlineStr">
+      <c r="AS27" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: Frog / topwater / moving bait / hard bait / worm / finesse; 样本路亚: ブレーバースリム8 (ボトムアップ) / 2WAY (レイドジャパン) , ジグヘッド0.9g</t>
         </is>
@@ -4369,12 +4401,13 @@
 The Defender can work a wide range of light rigs and plugs . Constructed as an un-sanded tubular blank with 4-axis carbon reinforcement, shaking is minimized for sharpness and high sensitivity. It covers everything known in bass fishing as "light-power (finesse) fishing" from small rubber jigs, Neko rigs, jighead wacky rigs, light jigheads, small shad baits, minnow jerkbaits, and topwater baits. While it's not tuned for a specific type of fishing or lure, the rod packs utility for exploring new or big waters with minimal gear or searching for the day's bite in your home waters. The name says it all and this one rod has you covered.</t>
         </is>
       </c>
-      <c r="AQ28" s="2" t="inlineStr">
+      <c r="AQ28" s="2" t="inlineStr"/>
+      <c r="AR28" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 7件; 场景: 霞ヶ浦 / 五三川 / 諏訪湖</t>
         </is>
       </c>
-      <c r="AR28" s="2" t="inlineStr">
+      <c r="AS28" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: 野良ネズミ (ティムコ) / レベルクランク ピング (レイドジャパン)</t>
         </is>
@@ -4496,12 +4529,13 @@
 ■マイクロダッジ(ハネあり、ハネ無し)、またエグダマTYPE-LEVELを使用した軽吊るしの釣りにベストマッチ。また、レベルバイブブースト(5g/7g)、ヘッドスイマーリベロ(5g/7g)にも対応。 ■強度を重視してFuji工業製ステンレスフレームSICガイド(Sタイプ)を採用。トップガイドにはチタンフレームSICガイドを採用。PEラインとリーダーの結束部(ノット)の抜けを良くするために、TOP~ベリーセクションには#5サイズのPKTSGを採用。</t>
         </is>
       </c>
-      <c r="AQ29" s="2" t="inlineStr">
+      <c r="AQ29" s="2" t="inlineStr"/>
+      <c r="AR29" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 6件; 场景: 琵琶湖 / 阿木川湖 / 君ヶ野ダム</t>
         </is>
       </c>
-      <c r="AR29" s="2" t="inlineStr">
+      <c r="AS29" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: スーパーフィッシュローラー 7インチ (レイドジャパン) / グリフォン ベイトフィネス MR-X (メガバス) , ワーミングクランクショット ディープ (ノリーズ)</t>
         </is>
@@ -4629,8 +4663,9 @@
 ■強度を重視してFuji工業製ステンレスフレームSICガイド(Sタイプ)を採用。トップガイドにはチタンフレームSICガイドを採用。</t>
         </is>
       </c>
-      <c r="AQ30" s="2" t="str"/>
+      <c r="AQ30" s="2" t="inlineStr"/>
       <c r="AR30" s="2" t="str"/>
+      <c r="AS30" s="2" t="str"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4748,12 +4783,13 @@
 The Stride is a spinning rod in the GLADIATOR Anti series for long distance tactics. With a specially constructed 6'11" blank with a slightly short 30t carbon solid tip, superior casting distance and control is achieved. Any movements that were previously undetectable on long distance casts can now be felt with high sensitivity and lures can easily be controlled. For use with light plugs and worms to metal vibrations to get reaction bites, the rod tip brings high sensitivity and control that truly breathes life into lures. Guides are tuned for both PE and fluorocarbon lines, allowing a stress-free cast every time. From casting, control, hookset, and landing, the rod is crafted to deliver the highest performance through the entire range of motions.</t>
         </is>
       </c>
-      <c r="AQ31" s="2" t="inlineStr">
+      <c r="AQ31" s="2" t="inlineStr"/>
+      <c r="AR31" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 6件; 场景: 霞ヶ浦水系 / 池 / 根井沼</t>
         </is>
       </c>
-      <c r="AR31" s="2" t="inlineStr">
+      <c r="AS31" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: ファットウィップ (レイドジャパン) / レベルバイブ ブースト , ファットウィップ 3インチ (レイドジャパン)</t>
         </is>
@@ -4875,12 +4911,13 @@
 ■強度を重視してFuji工業製ステンレスフレームSICガイド(Sタイプ)を採用。トップガイドにはチタンフレームSICガイドを採用。糸絡みによるブランクスの折損には十分にご注意ください。 ■パワーフィネスとして使用する際には、カバー内でバイトさせたバスへのダメージを最小限に抑える為、PEライン1.5号以上を使用してください。コシの無いPEラインには、ハリのある太めのフロロカーボンラインをリーダーに組むことで、カバーへの不要な絡みつきが減少しカバー内をストレスなく攻めることが可能になります。</t>
         </is>
       </c>
-      <c r="AQ32" s="2" t="inlineStr">
+      <c r="AQ32" s="2" t="inlineStr"/>
+      <c r="AR32" s="2" t="inlineStr">
         <is>
           <t>白名单样本: TackleDB 3件; 场景: 七色ダム / 竹馬川 / 柴山沼</t>
         </is>
       </c>
-      <c r="AR32" s="2" t="inlineStr">
+      <c r="AS32" s="2" t="inlineStr">
         <is>
           <t>白名单路亚信号: moving bait / hard bait / worm / finesse; 样本路亚: エグダマ タイプレベル 4.5g , サイコロラバー ノンソルト (O.S.P) / パドチュー (ノリーズ)</t>
         </is>
@@ -5010,8 +5047,9 @@
 ※1・・・2024年時点。</t>
         </is>
       </c>
-      <c r="AQ33" s="2" t="str"/>
+      <c r="AQ33" s="2" t="inlineStr"/>
       <c r="AR33" s="2" t="str"/>
+      <c r="AS33" s="2" t="str"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
